--- a/GameConfig/Datas/Defines/__tables__.xlsx
+++ b/GameConfig/Datas/Defines/__tables__.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub_Project\DGame\GameConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub_Project\DGame\GameConfig\Datas\Defines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6082D848-0039-4E6B-B635-337336EBE8BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688EE6E5-1A6B-42DD-93C9-3C5C6749D010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4940" yWindow="4940" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57525" yWindow="4815" windowWidth="28800" windowHeight="15375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -190,30 +190,6 @@
   </si>
   <si>
     <t>mode</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>TbSoundConfig1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SoundConfig1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效配置表1.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>TbSoundConfig2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SoundConfig2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>通用/音效配置表2.xlsx</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -573,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -781,40 +757,6 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
